--- a/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>34,84; 44,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>46,2; 56,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>63,22; 72,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>67,09; 75,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>74,06; 83,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>80,33; 88,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>83,38; 90,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>88,64; 94,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>51,67; 59,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>61,65; 68,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>73,57; 79,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>78,59; 83,59</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>41,75; 52,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>48,54; 59,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>60,09; 70,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>64,48; 73,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>79,8; 87,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>84,55; 92,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>90,17; 95,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>91,1; 96,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>62,35; 69,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>66,01; 73,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>75,98; 81,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>77,64; 83,46</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>30,06; 38,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>43,42; 51,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>50,95; 59,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>16,41; 67,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>82,41; 92,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>80,49; 90,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>85,58; 95,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>84,98; 94,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>43,16; 50,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>55,06; 61,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>60,55; 67,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>24,25; 74,34</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>30,8; 36,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>40,46; 46,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>50,43; 56,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>64,23; 70,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>83,36; 88,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>86,57; 91,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>88,08; 92,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>94,14; 97,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>50,08; 54,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>59,58; 64,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>66,69; 70,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,08</t>
+          <t>78,47; 87,33</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>30,99; 41,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>36,4; 44,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>42,01; 49,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>56,81; 66,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>87,85; 93,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>84,21; 89,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>89,12; 93,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>93,14; 96,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>66,53; 72,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>65,72; 70,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>68,0; 73,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>80,62; 86,51</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>8,26; 16,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>9,97; 18,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>19,99; 30,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>36,28; 57,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>78,41; 82,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>71,8; 77,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>76,99; 82,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>77,35; 83,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>64,82; 69,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>60,03; 65,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>65,75; 70,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>69,03; 76,51</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>32,4; 35,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>42,03; 45,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>51,24; 54,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>43,51; 66,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,74; 85,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,27; 84,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>86,24; 88,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,04</t>
+          <t>90,3; 93,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>58,36; 60,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>62,85; 65,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>69,53; 71,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,02</t>
+          <t>67,27; 80,06</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1791,62 +1791,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1028</t>
         </is>
       </c>
     </row>
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186489</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>361000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243403</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267673</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410776</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>429893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>771776</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1995</t>
+          <t>164755; 208422</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>201993; 244850</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2075</t>
+          <t>270662; 310504</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>338950; 380685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>227116; 257176</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>252586; 278970</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>289364; 314528</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1251</t>
+          <t>396025; 421260</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1988</t>
+          <t>402813; 461471</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>463423; 517971</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>570291; 618492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1474</t>
+          <t>748144; 795793</t>
         </is>
       </c>
     </row>
@@ -1999,62 +1999,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>561</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>463</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>895</t>
         </is>
       </c>
     </row>
@@ -2067,62 +2067,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172877</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226794</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>245917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312009</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300541</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>347635</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359996</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>484886</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>527334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673524</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>153204; 193048</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2138</t>
+          <t>203273; 247621</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>226659; 264437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1803</t>
+          <t>291292; 333847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1961</t>
+          <t>296758; 324874</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2120</t>
+          <t>285781; 311418</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2024</t>
+          <t>335676; 356291</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>348532; 367853</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1987</t>
+          <t>460666; 510543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2134</t>
+          <t>499565; 555733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>569436; 614225</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 1496</t>
+          <t>647732; 696309</t>
         </is>
       </c>
     </row>
@@ -2207,62 +2207,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>583</t>
         </is>
       </c>
     </row>
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>184940</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297866</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147842</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223118</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151704</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332782</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433212</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>163056; 207845</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>273282; 324419</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>264963; 309949</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2624</t>
+          <t>109684; 453787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>138263; 155405</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>209368; 234664</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>142161; 158002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1105</t>
+          <t>141368; 157380</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1956</t>
+          <t>306527; 360858</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>489790; 548983</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>415522; 466276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2063</t>
+          <t>202352; 620429</t>
         </is>
       </c>
     </row>
@@ -2415,62 +2415,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>467</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>716</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>991</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1905</t>
         </is>
       </c>
     </row>
@@ -2483,62 +2483,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>412155</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505454</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>612016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>614902</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>682180</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>741278</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>937664</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1027057</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1353293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1636174</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1941</t>
+          <t>381440; 448707</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2053</t>
+          <t>468898; 539488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>577588; 647473</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1776</t>
+          <t>664665; 731240</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1972</t>
+          <t>594156; 630365</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2068</t>
+          <t>661995; 699205</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>723894; 756945</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1526</t>
+          <t>920824; 957085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>977080; 1070074</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>1146139; 1231888</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1994</t>
+          <t>1311895; 1394072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1646</t>
+          <t>1579451; 1757817</t>
         </is>
       </c>
     </row>
@@ -2623,62 +2623,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>612</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1539</t>
         </is>
       </c>
     </row>
@@ -2691,62 +2691,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125316</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205953</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>515947</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>662679</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>674107</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>796658</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641263</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>959882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1091596</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1973</t>
+          <t>108639; 145524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>185450; 229096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>260778; 309816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1664</t>
+          <t>269891; 315728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2022</t>
+          <t>499667; 529464</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2077</t>
+          <t>641287; 680393</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>657094; 688837</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1252</t>
+          <t>783655; 807936</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>611653; 667104</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2051</t>
+          <t>835402; 901354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>923458; 993833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 1375</t>
+          <t>1061203; 1138782</t>
         </is>
       </c>
     </row>
@@ -2831,62 +2831,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>986</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>775</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>793</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1046</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2899,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35134</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36749</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>113863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003182</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>828439</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863117</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616204</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1038316</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>865189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>934484</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>730067</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>24620; 47934</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>26610; 50085</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>57025; 88028</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>87267; 138762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1936</t>
+          <t>976797; 1029210</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>796460; 855852</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>833006; 889872</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1260</t>
+          <t>588929; 636595</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>1000714; 1075250</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>826124; 902137</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2079</t>
+          <t>899011; 970145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1513</t>
+          <t>691627; 766542</t>
         </is>
       </c>
     </row>
@@ -3039,62 +3039,62 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6996</t>
         </is>
       </c>
     </row>
@@ -3107,62 +3107,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1116912</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1495841</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1793371</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2063371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2837285</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2964632</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3081373</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3272981</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3954197</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4460473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4874744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5336351</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>1059293; 1171713</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>1437884; 1562531</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2016</t>
+          <t>1730074; 1850809</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1965</t>
+          <t>1468582; 2249215</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>2791177; 2878835</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>2919030; 3009495</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>3041443; 3120157</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 1310</t>
+          <t>3229627; 3328191</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>3876930; 4033626</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2061</t>
+          <t>4379797; 4546260</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>4799950; 4947709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 1563</t>
+          <t>4676427; 5565956</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,84; 44,07</t>
+          <t>35,02; 44,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,2; 56,0</t>
+          <t>46,14; 56,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,22; 72,53</t>
+          <t>62,75; 72,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67,09; 75,35</t>
+          <t>67,06; 75,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,06; 83,86</t>
+          <t>74,63; 83,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,33; 88,72</t>
+          <t>80,97; 89,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,38; 90,63</t>
+          <t>83,07; 90,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,64; 94,29</t>
+          <t>89,26; 94,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,67; 59,2</t>
+          <t>51,21; 58,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,65; 68,91</t>
+          <t>61,63; 68,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,57; 79,79</t>
+          <t>73,31; 79,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,59; 83,59</t>
+          <t>78,17; 83,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,75; 52,61</t>
+          <t>41,44; 52,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,54; 59,13</t>
+          <t>48,78; 59,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,09; 70,1</t>
+          <t>60,19; 70,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,48; 73,9</t>
+          <t>64,85; 73,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,8; 87,36</t>
+          <t>79,59; 87,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,55; 92,13</t>
+          <t>84,98; 92,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,17; 95,71</t>
+          <t>90,59; 95,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,1; 96,15</t>
+          <t>91,32; 96,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,35; 69,1</t>
+          <t>62,08; 69,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,01; 73,43</t>
+          <t>65,74; 73,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,98; 81,95</t>
+          <t>75,62; 82,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,64; 83,46</t>
+          <t>77,98; 83,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 38,32</t>
+          <t>30,14; 38,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,42; 51,54</t>
+          <t>43,14; 51,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,95; 59,59</t>
+          <t>51,06; 59,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 67,91</t>
+          <t>60,46; 69,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,41; 92,62</t>
+          <t>82,18; 92,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,49; 90,21</t>
+          <t>80,74; 89,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,58; 95,11</t>
+          <t>85,69; 94,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,98; 94,61</t>
+          <t>85,06; 94,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,16; 50,81</t>
+          <t>43,08; 50,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,06; 61,72</t>
+          <t>54,9; 61,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,55; 67,95</t>
+          <t>60,29; 67,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,25; 74,34</t>
+          <t>68,42; 75,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,8; 36,23</t>
+          <t>30,47; 36,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 46,55</t>
+          <t>40,48; 46,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,43; 56,54</t>
+          <t>50,36; 56,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,23; 70,66</t>
+          <t>63,55; 69,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,36; 88,44</t>
+          <t>83,7; 88,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,57; 91,44</t>
+          <t>86,67; 91,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,08; 92,1</t>
+          <t>88,09; 92,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,14; 97,85</t>
+          <t>93,33; 96,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,08; 54,84</t>
+          <t>50,28; 54,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,58; 64,04</t>
+          <t>59,23; 63,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,69; 70,87</t>
+          <t>66,66; 71,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,47; 87,33</t>
+          <t>76,69; 80,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,51</t>
+          <t>30,62; 40,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,4; 44,96</t>
+          <t>35,87; 44,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,01; 49,91</t>
+          <t>41,78; 49,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56,81; 66,46</t>
+          <t>58,35; 67,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,85; 93,09</t>
+          <t>88,16; 93,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,21; 89,35</t>
+          <t>84,24; 89,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,12; 93,43</t>
+          <t>89,01; 93,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,14; 96,03</t>
+          <t>92,82; 95,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,53; 72,57</t>
+          <t>66,73; 72,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,72; 70,91</t>
+          <t>65,56; 70,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68,0; 73,18</t>
+          <t>68,07; 72,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,62; 86,51</t>
+          <t>79,24; 83,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,26; 16,07</t>
+          <t>8,3; 16,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,97; 18,77</t>
+          <t>9,94; 18,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,99; 30,85</t>
+          <t>20,32; 30,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,28; 57,7</t>
+          <t>35,09; 54,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78,41; 82,62</t>
+          <t>78,26; 82,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,8; 77,15</t>
+          <t>72,02; 77,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,99; 82,24</t>
+          <t>77,03; 82,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77,35; 83,61</t>
+          <t>77,78; 83,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64,82; 69,64</t>
+          <t>64,9; 69,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60,03; 65,55</t>
+          <t>60,09; 65,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65,75; 70,95</t>
+          <t>65,76; 70,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,03; 76,51</t>
+          <t>69,07; 76,43</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,4; 35,84</t>
+          <t>32,51; 35,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,03; 45,68</t>
+          <t>41,92; 45,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,24; 54,81</t>
+          <t>51,25; 54,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,51; 66,63</t>
+          <t>63,68; 67,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,74; 85,33</t>
+          <t>82,84; 85,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,27; 84,82</t>
+          <t>82,36; 84,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,24; 88,47</t>
+          <t>86,19; 88,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,3; 93,06</t>
+          <t>89,69; 91,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58,36; 60,72</t>
+          <t>58,27; 60,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62,85; 65,24</t>
+          <t>62,85; 65,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69,53; 71,67</t>
+          <t>69,5; 71,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,27; 80,06</t>
+          <t>77,21; 79,48</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361000</t>
+          <t>392403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>410776</t>
+          <t>449313</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>771776</t>
+          <t>841715</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>164755; 208422</t>
+          <t>165589; 209229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201993; 244850</t>
+          <t>201718; 246397</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>270662; 310504</t>
+          <t>268624; 309040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>338950; 380685</t>
+          <t>369266; 413799</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>227116; 257176</t>
+          <t>228870; 257121</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>252586; 278970</t>
+          <t>254619; 280045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>289364; 314528</t>
+          <t>288295; 315547</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>396025; 421260</t>
+          <t>435361; 460485</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>402813; 461471</t>
+          <t>399203; 456825</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>463423; 517971</t>
+          <t>463263; 517410</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>570291; 618492</t>
+          <t>568250; 617424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>748144; 795793</t>
+          <t>811652; 866176</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313528</t>
+          <t>335066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>359996</t>
+          <t>398221</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>673524</t>
+          <t>733287</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>153204; 193048</t>
+          <t>152047; 190941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>203273; 247621</t>
+          <t>204299; 248654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>226659; 264437</t>
+          <t>227036; 266495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>291292; 333847</t>
+          <t>313046; 356674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>296758; 324874</t>
+          <t>295980; 324517</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>285781; 311418</t>
+          <t>287244; 311313</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>335676; 356291</t>
+          <t>337258; 356891</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>348532; 367853</t>
+          <t>386415; 406390</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>460666; 510543</t>
+          <t>458667; 511303</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499565; 555733</t>
+          <t>497512; 553044</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>569436; 614225</t>
+          <t>566752; 615018</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>647732; 696309</t>
+          <t>706385; 756698</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281530</t>
+          <t>306191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>476449</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>163056; 207845</t>
+          <t>163464; 206143</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>273282; 324419</t>
+          <t>271520; 324407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264963; 309949</t>
+          <t>265554; 310130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109684; 453787</t>
+          <t>285141; 327254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>138263; 155405</t>
+          <t>137875; 155820</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>209368; 234664</t>
+          <t>210039; 233691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>142161; 158002</t>
+          <t>142354; 157669</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>141368; 157380</t>
+          <t>158993; 176688</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>306527; 360858</t>
+          <t>305933; 360537</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>489790; 548983</t>
+          <t>488385; 548883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>415522; 466276</t>
+          <t>413725; 466053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>202352; 620429</t>
+          <t>450598; 498268</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>755615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>937664</t>
+          <t>816354</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1636174</t>
+          <t>1571969</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>381440; 448707</t>
+          <t>377309; 447319</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>468898; 539488</t>
+          <t>469210; 539777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>577588; 647473</t>
+          <t>576739; 643512</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>664665; 731240</t>
+          <t>719293; 788114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>594156; 630365</t>
+          <t>596573; 631157</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>661995; 699205</t>
+          <t>662763; 700751</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>723894; 756945</t>
+          <t>723954; 757323</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>920824; 957085</t>
+          <t>803762; 828443</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977080; 1070074</t>
+          <t>981078; 1071883</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1146139; 1231888</t>
+          <t>1139314; 1229867</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1311895; 1394072</t>
+          <t>1311189; 1396948</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1579451; 1757817</t>
+          <t>1528568; 1609330</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294938</t>
+          <t>355993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>796658</t>
+          <t>782244</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1091596</t>
+          <t>1138237</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>108639; 145524</t>
+          <t>107348; 142973</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>185450; 229096</t>
+          <t>182758; 228633</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260778; 309816</t>
+          <t>259357; 308995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>269891; 315728</t>
+          <t>331387; 380813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>499667; 529464</t>
+          <t>501394; 530360</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>641287; 680393</t>
+          <t>641520; 678897</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>657094; 688837</t>
+          <t>656270; 688804</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>783655; 807936</t>
+          <t>771195; 791497</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>611653; 667104</t>
+          <t>613464; 668293</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>835402; 901354</t>
+          <t>833302; 900510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>923458; 993833</t>
+          <t>924327; 989597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1061203; 1138782</t>
+          <t>1108476; 1166959</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113863</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>616204</t>
+          <t>683574</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>730067</t>
+          <t>789217</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24620; 47934</t>
+          <t>24754; 47846</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26610; 50085</t>
+          <t>26524; 49261</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57025; 88028</t>
+          <t>57983; 87285</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87267; 138762</t>
+          <t>83232; 128102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>976797; 1029210</t>
+          <t>974956; 1029929</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>796460; 855852</t>
+          <t>798915; 856026</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>833006; 889872</t>
+          <t>833523; 892987</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>588929; 636595</t>
+          <t>656695; 709123</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1000714; 1075250</t>
+          <t>1001938; 1073328</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>826124; 902137</t>
+          <t>827022; 898411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>899011; 970145</t>
+          <t>899191; 969104</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>691627; 766542</t>
+          <t>746972; 826605</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2063371</t>
+          <t>2250911</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3272981</t>
+          <t>3299966</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5336351</t>
+          <t>5550875</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1059293; 1171713</t>
+          <t>1062992; 1173507</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1437884; 1562531</t>
+          <t>1434165; 1554984</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1730074; 1850809</t>
+          <t>1730418; 1853055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1468582; 2249215</t>
+          <t>2191844; 2315368</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2791177; 2878835</t>
+          <t>2794539; 2878009</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2919030; 3009495</t>
+          <t>2922088; 3006707</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3041443; 3120157</t>
+          <t>3039488; 3122705</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3229627; 3328191</t>
+          <t>3259600; 3334112</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3876930; 4033626</t>
+          <t>3870724; 4033126</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4379797; 4546260</t>
+          <t>4380285; 4541938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4799950; 4947709</t>
+          <t>4798002; 4950614</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4676427; 5565956</t>
+          <t>5463609; 5624402</t>
         </is>
       </c>
     </row>
